--- a/res/excel/loadplan_template/load_plan_template.xlsx
+++ b/res/excel/loadplan_template/load_plan_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aldri\OneDrive\Desktop\Nikka System\WLP_Automation-v7\res\excel\loadplan_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13D68677-335B-4A16-9C0B-123C817A151F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4640C5E-29C9-419D-9BA0-BFDF69D2E328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{E31B4C9E-2B2E-4045-962C-05F8A6B83FCC}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="88">
   <si>
     <t>NIKKA TRADING</t>
   </si>
@@ -162,9 +162,6 @@
     <t>Documents Released by</t>
   </si>
   <si>
-    <t xml:space="preserve">RODJAN FAT               </t>
-  </si>
-  <si>
     <t xml:space="preserve">JASON OLILA              </t>
   </si>
   <si>
@@ -220,9 +217,6 @@
   </si>
   <si>
     <t>Put a stamp once released                           and once received.</t>
-  </si>
-  <si>
-    <t>ANGELICA DOMULOT</t>
   </si>
   <si>
     <t>Asst. Logistics Financial Analyst</t>
@@ -275,13 +269,40 @@
   </si>
   <si>
     <t>Remarks</t>
+  </si>
+  <si>
+    <t>DEPED</t>
+  </si>
+  <si>
+    <t>Time created:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control No: DEPED - R - mm/dd/yy-1001 </t>
+  </si>
+  <si>
+    <t># Region</t>
+  </si>
+  <si>
+    <t>Mass Production, Supply, and Delivery of Science and Mathematics Equipment Packages to Public Elementary Schools for Grades 1 to 3 and Grades 4 to 6, Public Junior High Schools for Grades 7 to 10, and Public Senior High Schools for Grades 11 to 12 (EARLY PROCUREMENT ACTIVITY 2024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JENNETH LAUDE                </t>
+  </si>
+  <si>
+    <t>Documentation Lead-in-charge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANGELICA DOMULOT         </t>
+  </si>
+  <si>
+    <t>Region</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -405,8 +426,15 @@
       <name val="AriaL"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="AriaL"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -421,55 +449,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.749992370372631"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFF9999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB484E8"/>
+        <fgColor rgb="FFD9ED92"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D98C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34A0A4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A759F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E48C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF168AAD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E6091"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -695,7 +729,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -792,48 +826,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -846,34 +838,132 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -884,116 +974,68 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1003,16 +1045,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFB484E8"/>
-      <color rgb="FFFF9999"/>
-      <color rgb="FF6FD984"/>
-      <color rgb="FFFFC09F"/>
-      <color rgb="FFFFFF99"/>
-      <color rgb="FFFFFFCC"/>
-      <color rgb="FFADF7B6"/>
-      <color rgb="FFA0CED9"/>
-      <color rgb="FFFCF5C7"/>
-      <color rgb="FFFFEE93"/>
+      <color rgb="FF1E6091"/>
+      <color rgb="FF184E77"/>
+      <color rgb="FF1A759F"/>
+      <color rgb="FF168AAD"/>
+      <color rgb="FF34A0A4"/>
+      <color rgb="FF76C893"/>
+      <color rgb="FF99D98C"/>
+      <color rgb="FFB5E48C"/>
+      <color rgb="FFD9ED92"/>
+      <color rgb="FF7C93C3"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1362,119 +1404,124 @@
     <col min="18" max="16384" width="10.8984375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="68" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="G1" s="64" t="s">
+    <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="78" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="69" t="s">
+      <c r="E1" s="57" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="14"/>
+      <c r="H1" s="82" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1" s="82"/>
+      <c r="J1" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="69"/>
-      <c r="L1" s="62" t="s">
+      <c r="K1" s="79"/>
+      <c r="M1" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="68"/>
+      <c r="P1" s="68"/>
+      <c r="Q1" s="68"/>
     </row>
     <row r="2" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="67" t="s">
+      <c r="C2" s="84"/>
+      <c r="D2" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="61" t="s">
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="85"/>
+      <c r="L2" s="85"/>
+      <c r="M2" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
+      <c r="N2" s="76"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
     </row>
     <row r="3" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="66"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="67"/>
-      <c r="M3" s="61"/>
-      <c r="N3" s="61"/>
-      <c r="O3" s="61"/>
-      <c r="P3" s="61"/>
-      <c r="Q3" s="61"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
+      <c r="L3" s="85"/>
+      <c r="M3" s="76"/>
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
     </row>
     <row r="4" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="66"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="70" t="s">
+      <c r="B4" s="84"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="70"/>
-      <c r="K4" s="70"/>
-      <c r="L4" s="70"/>
-      <c r="M4" s="63" t="s">
-        <v>19</v>
-      </c>
-      <c r="N4" s="63"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="80"/>
+      <c r="L4" s="80"/>
+      <c r="M4" s="106" t="s">
+        <v>87</v>
+      </c>
+      <c r="N4" s="106"/>
+      <c r="O4" s="106"/>
+      <c r="P4" s="106"/>
+      <c r="Q4" s="106"/>
     </row>
     <row r="5" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="66"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
-      <c r="L5" s="70"/>
-      <c r="M5" s="63"/>
-      <c r="N5" s="63"/>
-      <c r="O5" s="63"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
+      <c r="B5" s="84"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="80"/>
+      <c r="L5" s="80"/>
+      <c r="M5" s="106"/>
+      <c r="N5" s="106"/>
+      <c r="O5" s="106"/>
+      <c r="P5" s="106"/>
+      <c r="Q5" s="106"/>
     </row>
     <row r="6" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="65" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="3"/>
+      <c r="B6" s="83" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="61"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -1489,25 +1536,25 @@
       <c r="Q6" s="3"/>
     </row>
     <row r="7" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="65"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="65"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
       <c r="E7" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="71" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="71"/>
-      <c r="H7" s="71"/>
-      <c r="I7" s="71"/>
-      <c r="J7" s="71"/>
-      <c r="K7" s="71"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="72" t="s">
+      <c r="F7" s="81" t="s">
+        <v>81</v>
+      </c>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="81"/>
+      <c r="K7" s="81"/>
+      <c r="L7" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="N7" s="72"/>
+      <c r="M7" s="75"/>
+      <c r="N7" s="75"/>
       <c r="O7" s="18" t="s">
         <v>21</v>
       </c>
@@ -1515,172 +1562,172 @@
       <c r="Q7"/>
     </row>
     <row r="8" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="60" t="s">
-        <v>57</v>
-      </c>
-      <c r="B8" s="60"/>
-      <c r="C8" s="60"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="60"/>
-      <c r="K8" s="60"/>
-      <c r="L8" s="60"/>
-      <c r="M8" s="60"/>
-      <c r="N8" s="60"/>
-      <c r="O8" s="60"/>
-      <c r="P8" s="60"/>
-      <c r="Q8" s="60"/>
+      <c r="A8" s="66" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="66"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="66"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="66"/>
+      <c r="M8" s="66"/>
+      <c r="N8" s="66"/>
+      <c r="O8" s="66"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66"/>
     </row>
     <row r="9" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="60"/>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="60"/>
-      <c r="K9" s="60"/>
-      <c r="L9" s="60"/>
-      <c r="M9" s="60"/>
-      <c r="N9" s="60"/>
-      <c r="O9" s="60"/>
-      <c r="P9" s="60"/>
-      <c r="Q9" s="60"/>
+      <c r="A9" s="66"/>
+      <c r="B9" s="66"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="66"/>
+      <c r="J9" s="66"/>
+      <c r="K9" s="66"/>
+      <c r="L9" s="66"/>
+      <c r="M9" s="66"/>
+      <c r="N9" s="66"/>
+      <c r="O9" s="66"/>
+      <c r="P9" s="66"/>
+      <c r="Q9" s="66"/>
     </row>
     <row r="10" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="60"/>
-      <c r="B10" s="60"/>
-      <c r="C10" s="60"/>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="60"/>
-      <c r="J10" s="60"/>
-      <c r="K10" s="60"/>
-      <c r="L10" s="60"/>
-      <c r="M10" s="60"/>
-      <c r="N10" s="60"/>
-      <c r="O10" s="60"/>
-      <c r="P10" s="60"/>
-      <c r="Q10" s="60"/>
+      <c r="A10" s="66"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
+      <c r="J10" s="66"/>
+      <c r="K10" s="66"/>
+      <c r="L10" s="66"/>
+      <c r="M10" s="66"/>
+      <c r="N10" s="66"/>
+      <c r="O10" s="66"/>
+      <c r="P10" s="66"/>
+      <c r="Q10" s="66"/>
     </row>
     <row r="11" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="73" t="s">
+      <c r="A11" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="59" t="s">
+      <c r="B11" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="59" t="s">
+      <c r="D11" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="74" t="s">
+      <c r="E11" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="77" t="s">
+      <c r="F11" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="G11" s="80" t="s">
+      <c r="G11" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="81"/>
-      <c r="I11" s="81"/>
-      <c r="J11" s="81"/>
-      <c r="K11" s="81"/>
-      <c r="L11" s="81"/>
-      <c r="M11" s="81"/>
-      <c r="N11" s="82"/>
-      <c r="O11" s="59" t="s">
+      <c r="H11" s="73"/>
+      <c r="I11" s="73"/>
+      <c r="J11" s="73"/>
+      <c r="K11" s="73"/>
+      <c r="L11" s="73"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="65" t="s">
+        <v>68</v>
+      </c>
+      <c r="P11" s="65" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q11" s="65" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="67"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="L12" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="M12" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="O12" s="65"/>
+      <c r="P12" s="65"/>
+      <c r="Q12" s="65"/>
+    </row>
+    <row r="13" spans="1:17" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A13" s="67"/>
+      <c r="B13" s="65"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="42" t="s">
         <v>70</v>
       </c>
-      <c r="P11" s="59" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q11" s="59" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="73"/>
-      <c r="B12" s="59"/>
-      <c r="C12" s="59"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="75"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="I12" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="J12" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="K12" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="L12" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="M12" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="N12" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="O12" s="59"/>
-      <c r="P12" s="59"/>
-      <c r="Q12" s="59"/>
-    </row>
-    <row r="13" spans="1:17" ht="20.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A13" s="73"/>
-      <c r="B13" s="59"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="76"/>
-      <c r="F13" s="79"/>
-      <c r="G13" s="45" t="s">
-        <v>72</v>
-      </c>
-      <c r="H13" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="I13" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="J13" s="58" t="s">
-        <v>72</v>
-      </c>
-      <c r="K13" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="L13" s="41" t="s">
-        <v>72</v>
-      </c>
-      <c r="M13" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="N13" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="O13" s="59"/>
-      <c r="P13" s="59"/>
-      <c r="Q13" s="59"/>
+      <c r="H13" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="I13" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="J13" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="K13" s="48" t="s">
+        <v>70</v>
+      </c>
+      <c r="L13" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="M13" s="50" t="s">
+        <v>70</v>
+      </c>
+      <c r="N13" s="56" t="s">
+        <v>70</v>
+      </c>
+      <c r="O13" s="65"/>
+      <c r="P13" s="65"/>
+      <c r="Q13" s="65"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
@@ -1703,33 +1750,33 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="D4:L5"/>
+    <mergeCell ref="F7:K7"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="B6:D7"/>
+    <mergeCell ref="B2:C5"/>
+    <mergeCell ref="D2:L3"/>
+    <mergeCell ref="M1:Q1"/>
     <mergeCell ref="O11:O13"/>
     <mergeCell ref="F11:F13"/>
     <mergeCell ref="G11:N11"/>
     <mergeCell ref="P11:P13"/>
     <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="M2:Q3"/>
+    <mergeCell ref="M4:Q5"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
     <mergeCell ref="A8:Q10"/>
-    <mergeCell ref="M2:Q3"/>
-    <mergeCell ref="L1:Q1"/>
-    <mergeCell ref="M4:Q5"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="B6:D7"/>
-    <mergeCell ref="B2:C5"/>
-    <mergeCell ref="D2:L3"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="D4:L5"/>
-    <mergeCell ref="F7:K7"/>
-    <mergeCell ref="M7:N7"/>
     <mergeCell ref="A11:A13"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="153" scale="98" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="153" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
@@ -1738,9 +1785,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F57B99B-51F3-4BAF-90D5-6F232EC3A8AD}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:O35"/>
   <sheetFormatPr defaultColWidth="10.8984375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1865,10 +1909,10 @@
       <c r="B8" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="83" t="s">
+      <c r="C8" s="103" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="83"/>
+      <c r="D8" s="103"/>
       <c r="E8" s="23" t="s">
         <v>15</v>
       </c>
@@ -1881,10 +1925,10 @@
     </row>
     <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="22"/>
-      <c r="C9" s="84" t="s">
+      <c r="C9" s="86" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="84"/>
+      <c r="D9" s="86"/>
       <c r="E9" s="24"/>
       <c r="G9" s="15"/>
       <c r="H9" s="15"/>
@@ -1902,35 +1946,35 @@
       <c r="L10" s="15"/>
     </row>
     <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="86"/>
+      <c r="A11" s="91"/>
       <c r="B11" s="22"/>
-      <c r="C11" s="83" t="s">
+      <c r="C11" s="103" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="83"/>
+      <c r="D11" s="103"/>
       <c r="E11" s="23" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="86"/>
+      <c r="A12" s="91"/>
       <c r="B12" s="12"/>
-      <c r="C12" s="85" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" s="85"/>
+      <c r="C12" s="88" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="88"/>
       <c r="E12" s="24"/>
     </row>
     <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="86"/>
+      <c r="A13" s="91"/>
     </row>
     <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="25"/>
       <c r="B14" s="12"/>
-      <c r="C14" s="83" t="s">
+      <c r="C14" s="103" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="83"/>
+      <c r="D14" s="103"/>
       <c r="E14" s="23" t="s">
         <v>15</v>
       </c>
@@ -1943,10 +1987,10 @@
     </row>
     <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10"/>
-      <c r="C15" s="84" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" s="84"/>
+      <c r="C15" s="86" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="86"/>
       <c r="E15" s="24"/>
       <c r="O15" s="22"/>
     </row>
@@ -1957,13 +2001,13 @@
       </c>
       <c r="H16" s="87"/>
       <c r="I16" s="87"/>
-      <c r="J16" s="83" t="s">
-        <v>44</v>
-      </c>
-      <c r="K16" s="83"/>
-      <c r="L16" s="83"/>
+      <c r="J16" s="103" t="s">
+        <v>84</v>
+      </c>
+      <c r="K16" s="103"/>
+      <c r="L16" s="103"/>
       <c r="M16" s="87" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N16" s="87"/>
       <c r="O16" s="87"/>
@@ -1973,25 +2017,25 @@
       <c r="B17" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="83" t="s">
+      <c r="C17" s="103" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="83"/>
+      <c r="D17" s="103"/>
       <c r="E17" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="J17" s="84" t="s">
-        <v>68</v>
-      </c>
-      <c r="K17" s="84"/>
-      <c r="L17" s="84"/>
+      <c r="J17" s="86" t="s">
+        <v>85</v>
+      </c>
+      <c r="K17" s="86"/>
+      <c r="L17" s="86"/>
     </row>
     <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10"/>
-      <c r="C18" s="84" t="s">
+      <c r="C18" s="86" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="84"/>
+      <c r="D18" s="86"/>
       <c r="O18" s="22"/>
     </row>
     <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2001,38 +2045,38 @@
       </c>
       <c r="H19" s="87"/>
       <c r="I19" s="87"/>
-      <c r="J19" s="83" t="s">
-        <v>45</v>
-      </c>
-      <c r="K19" s="83"/>
-      <c r="L19" s="83"/>
+      <c r="J19" s="103" t="s">
+        <v>44</v>
+      </c>
+      <c r="K19" s="103"/>
+      <c r="L19" s="103"/>
       <c r="M19" s="87" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N19" s="87"/>
       <c r="O19" s="87"/>
     </row>
     <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10"/>
-      <c r="C20" s="83" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" s="83"/>
+      <c r="C20" s="103" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="103"/>
       <c r="E20" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="J20" s="84" t="s">
-        <v>68</v>
-      </c>
-      <c r="K20" s="84"/>
-      <c r="L20" s="84"/>
+      <c r="J20" s="86" t="s">
+        <v>66</v>
+      </c>
+      <c r="K20" s="86"/>
+      <c r="L20" s="86"/>
     </row>
     <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
-      <c r="C21" s="85" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" s="85"/>
+      <c r="C21" s="88" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="88"/>
     </row>
     <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10"/>
@@ -2043,7 +2087,7 @@
       <c r="K22" s="21"/>
       <c r="L22" s="21"/>
       <c r="M22" s="87" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N22" s="87"/>
       <c r="O22" s="87"/>
@@ -2051,12 +2095,12 @@
     <row r="23" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10"/>
       <c r="B23" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="83" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="83"/>
+        <v>45</v>
+      </c>
+      <c r="C23" s="103" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="103"/>
       <c r="E23" s="23" t="s">
         <v>15</v>
       </c>
@@ -2070,7 +2114,7 @@
     <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12"/>
       <c r="C24" s="26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D24" s="26"/>
       <c r="G24" s="21"/>
@@ -2079,11 +2123,11 @@
       <c r="J24" s="21"/>
       <c r="K24" s="21"/>
       <c r="L24" s="21"/>
-      <c r="M24" s="89" t="s">
-        <v>63</v>
-      </c>
-      <c r="N24" s="90"/>
-      <c r="O24" s="91"/>
+      <c r="M24" s="93" t="s">
+        <v>62</v>
+      </c>
+      <c r="N24" s="94"/>
+      <c r="O24" s="95"/>
     </row>
     <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12"/>
@@ -2093,119 +2137,120 @@
       <c r="J25" s="21"/>
       <c r="K25" s="21"/>
       <c r="L25" s="21"/>
-      <c r="M25" s="92"/>
-      <c r="N25" s="93"/>
-      <c r="O25" s="94"/>
+      <c r="M25" s="96"/>
+      <c r="N25" s="97"/>
+      <c r="O25" s="98"/>
     </row>
     <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M26" s="92"/>
-      <c r="N26" s="93"/>
-      <c r="O26" s="94"/>
+      <c r="M26" s="96"/>
+      <c r="N26" s="97"/>
+      <c r="O26" s="98"/>
     </row>
     <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="87" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C27" s="87"/>
       <c r="E27" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="H27" s="88" t="s">
-        <v>49</v>
-      </c>
-      <c r="I27" s="88"/>
+        <v>51</v>
+      </c>
+      <c r="H27" s="92" t="s">
+        <v>48</v>
+      </c>
+      <c r="I27" s="92"/>
       <c r="L27" s="32"/>
-      <c r="M27" s="92"/>
-      <c r="N27" s="93"/>
-      <c r="O27" s="94"/>
+      <c r="M27" s="96"/>
+      <c r="N27" s="97"/>
+      <c r="O27" s="98"/>
     </row>
     <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E28" s="35"/>
       <c r="F28" s="35"/>
       <c r="L28" s="33"/>
-      <c r="M28" s="92"/>
-      <c r="N28" s="93"/>
-      <c r="O28" s="94"/>
+      <c r="M28" s="96"/>
+      <c r="N28" s="97"/>
+      <c r="O28" s="98"/>
     </row>
     <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="98" t="s">
+      <c r="B29" s="90" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="90"/>
+      <c r="D29" s="90"/>
+      <c r="E29" s="90" t="s">
+        <v>59</v>
+      </c>
+      <c r="F29" s="90"/>
+      <c r="G29" s="90"/>
+      <c r="H29" s="90" t="s">
+        <v>60</v>
+      </c>
+      <c r="I29" s="90"/>
+      <c r="J29" s="90"/>
+      <c r="K29" s="90"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="96"/>
+      <c r="N29" s="97"/>
+      <c r="O29" s="98"/>
+    </row>
+    <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="102" t="s">
         <v>55</v>
       </c>
-      <c r="C29" s="98"/>
-      <c r="D29" s="98"/>
-      <c r="E29" s="98" t="s">
-        <v>60</v>
-      </c>
-      <c r="F29" s="98"/>
-      <c r="G29" s="98"/>
-      <c r="H29" s="98" t="s">
-        <v>61</v>
-      </c>
-      <c r="I29" s="98"/>
-      <c r="J29" s="98"/>
-      <c r="K29" s="98"/>
-      <c r="L29" s="33"/>
-      <c r="M29" s="92"/>
-      <c r="N29" s="93"/>
-      <c r="O29" s="94"/>
-    </row>
-    <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="99" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" s="99"/>
-      <c r="D30" s="99"/>
-      <c r="E30" s="99" t="s">
+      <c r="C30" s="102"/>
+      <c r="D30" s="102"/>
+      <c r="E30" s="102" t="s">
+        <v>49</v>
+      </c>
+      <c r="F30" s="102"/>
+      <c r="G30" s="102"/>
+      <c r="H30" s="102" t="s">
+        <v>47</v>
+      </c>
+      <c r="I30" s="102"/>
+      <c r="J30" s="102"/>
+      <c r="K30" s="102"/>
+      <c r="L30" s="34"/>
+      <c r="M30" s="96"/>
+      <c r="N30" s="97"/>
+      <c r="O30" s="98"/>
+    </row>
+    <row r="31" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="89" t="s">
         <v>50</v>
       </c>
-      <c r="F30" s="99"/>
-      <c r="G30" s="99"/>
-      <c r="H30" s="99" t="s">
-        <v>48</v>
-      </c>
-      <c r="I30" s="99"/>
-      <c r="J30" s="99"/>
-      <c r="K30" s="99"/>
-      <c r="L30" s="34"/>
-      <c r="M30" s="92"/>
-      <c r="N30" s="93"/>
-      <c r="O30" s="94"/>
-    </row>
-    <row r="31" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="100" t="s">
-        <v>51</v>
-      </c>
-      <c r="C31" s="100"/>
-      <c r="D31" s="100"/>
-      <c r="E31" s="100" t="s">
-        <v>51</v>
-      </c>
-      <c r="F31" s="100"/>
-      <c r="G31" s="100"/>
-      <c r="H31" s="100" t="s">
-        <v>51</v>
-      </c>
-      <c r="I31" s="100"/>
-      <c r="J31" s="100"/>
-      <c r="K31" s="100"/>
+      <c r="C31" s="89"/>
+      <c r="D31" s="89"/>
+      <c r="E31" s="89" t="s">
+        <v>50</v>
+      </c>
+      <c r="F31" s="89"/>
+      <c r="G31" s="89"/>
+      <c r="H31" s="89" t="s">
+        <v>50</v>
+      </c>
+      <c r="I31" s="89"/>
+      <c r="J31" s="89"/>
+      <c r="K31" s="89"/>
       <c r="L31" s="23"/>
-      <c r="M31" s="95"/>
-      <c r="N31" s="96"/>
-      <c r="O31" s="97"/>
+      <c r="M31" s="99"/>
+      <c r="N31" s="100"/>
+      <c r="O31" s="101"/>
     </row>
     <row r="32" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="24.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="J17:L17"/>
-    <mergeCell ref="J20:L20"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="H31:K31"/>
-    <mergeCell ref="E31:G31"/>
-    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C18:D18"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="M22:O22"/>
     <mergeCell ref="G16:I16"/>
@@ -2222,18 +2267,17 @@
     <mergeCell ref="M19:O19"/>
     <mergeCell ref="J16:L16"/>
     <mergeCell ref="J19:L19"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="H31:K31"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="E29:G29"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="153" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="10000" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2261,110 +2305,116 @@
     <col min="16" max="16384" width="10.8984375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="68" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="G1" s="64" t="s">
+    <row r="1" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="78" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="69" t="s">
+      <c r="E1" s="57" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="59"/>
+      <c r="H1" s="60" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="69"/>
-      <c r="L1" s="62" t="s">
+      <c r="J1" s="79"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="68"/>
     </row>
     <row r="2" spans="1:15" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="67" t="s">
+      <c r="C2" s="84"/>
+      <c r="D2" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="61" t="s">
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="85"/>
+      <c r="L2" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
+      <c r="M2" s="76"/>
+      <c r="N2" s="76"/>
+      <c r="O2" s="76"/>
     </row>
     <row r="3" spans="1:15" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="66"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="67"/>
-      <c r="M3" s="61"/>
-      <c r="N3" s="61"/>
-      <c r="O3" s="61"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
+      <c r="L3" s="76"/>
+      <c r="M3" s="76"/>
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
     </row>
     <row r="4" spans="1:15" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="66"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="70" t="s">
+      <c r="B4" s="84"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="70"/>
-      <c r="K4" s="70"/>
-      <c r="L4" s="70"/>
-      <c r="M4" s="63" t="s">
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="80"/>
+      <c r="L4" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="63"/>
-      <c r="O4" s="63"/>
+      <c r="M4" s="77"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
     </row>
     <row r="5" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="66"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
-      <c r="L5" s="70"/>
-      <c r="M5" s="63"/>
-      <c r="N5" s="63"/>
-      <c r="O5" s="63"/>
+      <c r="B5" s="84"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="80"/>
+      <c r="L5" s="77"/>
+      <c r="M5" s="77"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
     </row>
     <row r="6" spans="1:15" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="65" t="s">
+      <c r="B6" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="54" t="s">
-        <v>73</v>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="40" t="s">
+        <v>71</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -2377,124 +2427,124 @@
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
     </row>
-    <row r="7" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="65"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="65"/>
+    <row r="7" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="83"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
       <c r="E7" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="103" t="s">
+      <c r="F7" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="103"/>
-      <c r="H7" s="103"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="104" t="s">
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="81"/>
+      <c r="K7" s="81"/>
+      <c r="L7" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="K7" s="104"/>
-      <c r="L7" s="104"/>
-      <c r="M7" s="56" t="s">
+      <c r="M7" s="75"/>
+      <c r="N7" s="75"/>
+      <c r="O7" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="N7" s="56"/>
-      <c r="O7"/>
     </row>
     <row r="8" spans="1:15" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="60" t="s">
-        <v>57</v>
-      </c>
-      <c r="B8" s="60"/>
-      <c r="C8" s="60"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="60"/>
-      <c r="K8" s="60"/>
-      <c r="L8" s="60"/>
-      <c r="M8" s="60"/>
-      <c r="N8" s="60"/>
-      <c r="O8" s="60"/>
+      <c r="A8" s="66" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="66"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="66"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="66"/>
+      <c r="M8" s="66"/>
+      <c r="N8" s="66"/>
+      <c r="O8" s="66"/>
     </row>
     <row r="9" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="60"/>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="60"/>
-      <c r="K9" s="60"/>
-      <c r="L9" s="60"/>
-      <c r="M9" s="60"/>
-      <c r="N9" s="60"/>
-      <c r="O9" s="60"/>
+      <c r="A9" s="66"/>
+      <c r="B9" s="66"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="66"/>
+      <c r="J9" s="66"/>
+      <c r="K9" s="66"/>
+      <c r="L9" s="66"/>
+      <c r="M9" s="66"/>
+      <c r="N9" s="66"/>
+      <c r="O9" s="66"/>
     </row>
     <row r="10" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="60"/>
-      <c r="B10" s="60"/>
-      <c r="C10" s="60"/>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="60"/>
-      <c r="J10" s="60"/>
-      <c r="K10" s="60"/>
-      <c r="L10" s="60"/>
-      <c r="M10" s="60"/>
-      <c r="N10" s="60"/>
-      <c r="O10" s="60"/>
+      <c r="A10" s="66"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
+      <c r="J10" s="66"/>
+      <c r="K10" s="66"/>
+      <c r="L10" s="66"/>
+      <c r="M10" s="66"/>
+      <c r="N10" s="66"/>
+      <c r="O10" s="66"/>
     </row>
     <row r="11" spans="1:15" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="53" t="s">
+      <c r="A11" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="C11" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="51" t="s">
+      <c r="D11" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="50" t="s">
+      <c r="E11" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="52" t="s">
+      <c r="F11" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="G11" s="52" t="s">
+      <c r="G11" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="I11" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="H11" s="52" t="s">
+      <c r="J11" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="I11" s="52" t="s">
+      <c r="K11" s="72" t="s">
         <v>76</v>
       </c>
-      <c r="J11" s="52" t="s">
+      <c r="L11" s="74"/>
+      <c r="M11" s="72" t="s">
         <v>77</v>
       </c>
-      <c r="K11" s="80" t="s">
+      <c r="N11" s="74"/>
+      <c r="O11" s="37" t="s">
         <v>78</v>
-      </c>
-      <c r="L11" s="82"/>
-      <c r="M11" s="80" t="s">
-        <v>79</v>
-      </c>
-      <c r="N11" s="82"/>
-      <c r="O11" s="51" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -2508,35 +2558,34 @@
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
-      <c r="K12" s="101"/>
-      <c r="L12" s="102"/>
-      <c r="M12" s="101"/>
-      <c r="N12" s="102"/>
+      <c r="K12" s="104"/>
+      <c r="L12" s="105"/>
+      <c r="M12" s="104"/>
+      <c r="N12" s="105"/>
       <c r="O12" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="K12:L12"/>
+  <mergeCells count="16">
     <mergeCell ref="B6:D7"/>
     <mergeCell ref="A8:O10"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="J1:K1"/>
     <mergeCell ref="L1:O1"/>
     <mergeCell ref="B2:C5"/>
-    <mergeCell ref="D2:L3"/>
-    <mergeCell ref="M2:O3"/>
-    <mergeCell ref="D4:L5"/>
-    <mergeCell ref="M4:O5"/>
+    <mergeCell ref="D4:K5"/>
+    <mergeCell ref="L4:O5"/>
+    <mergeCell ref="D2:K3"/>
+    <mergeCell ref="L2:O3"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="F7:K7"/>
+    <mergeCell ref="L7:N7"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="153" scale="91" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="10000" scale="93" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
